--- a/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-FILLSGAP-PROBE.xlsx
+++ b/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-FILLSGAP-PROBE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary &amp; Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidates'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidates'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -444,7 +444,11 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,11 +484,31 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Catalogue says</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bibliography says</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PGP says</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>FGP says</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Why this row is in the set</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -511,11 +535,31 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>קבץ קטעי גניזה.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -542,11 +586,31 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>קטעי גניזה : ; קטעים תחת זכוכית.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -573,11 +637,31 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>דף שטיח.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -604,11 +688,31 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>JQR To JQR Vol. 5 pp. 443-52 מרמורשטין, אברהם Marmorstein, Arthur---JQR OS Schechter, Solomon---JQR OS Saadyana---A history of Palestine, 634-1099 History of Palestine גיל, משה Gil, Moshe---Palestine during the First Muslim Period (634-1099). ארץ ישראל בתקופה המוסלמית הראשונה (1099-634) גיל, משה Gil, Moshe---Palestine during the first Muslim period (634-1099). ארץ ישראל בתקופה המוסלמית הראשונה (1099-634) ארץ-ישראל בתקופה המוסלמית הראשונה Palestine גיל, משה Gil, Moshe---Saadyana. Geniza fragments of writings of R. Saadya Gaon and others (XII) Saadyana (XII) Schechter, Solomon---Saadyana. Geniza fragments of writings of R. Saadya Gaon and others (XII) Saadyana (XII) Schechter, Solomon---Saadyana. Geniza fragments of writings of R. Saadya Gaon and others (XII) Saadyana (XII) Schechter, Solomon</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -635,11 +739,31 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>פרשנות מקרא. ; Commentary relating to the Tabernacle in various biblical passages</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>AJAM-OS</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -666,11 +790,31 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>הלכה. ; דיון על זכויות של יהודים בעלי מעמדות שונים - כהנים, לויים, וכו'.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>כתבי יד רבניים Rabbinic Manuscripts---AJAM-NS Arabic and Judaeo-Arabic manuscripts in the Cambridge Genizah Collections: Taylor-Schechter new series---Verbal morphology in the Karaite treatise on Hebrew grammar Kitab al-Uqud fi tasarif al-Luga al-Ibraniyya Verbal morphology Vidro, Nadia</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="130" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -697,11 +841,31 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>מקרא ותרגומים;פרשנות מקרא;פרשנות מקרא רבנית. ; Biblical Exegesis ; Commentary, including a discussion on metaphors, quoting biblical sources (Genesis 28:12; Proverbs 7:10-21)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>AJAM-NS Arabic and Judaeo-Arabic manuscripts in the Cambridge Genizah Collections: Taylor-Schechter new series</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="130" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -728,11 +892,31 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Kiryat Sefer: Bibliographical Quaterly of the Jewish National and University Library קרית ספר: רבעון ביבליוגרפי של בית הספרים הלאומי והאוניברסיטאי בירושלים קרית ספר Kiryat Sefer מי הדפיס את ההגדה המצוייה הראשונה? שרמר, עדיאל Schremer, Adiel---Targum Onkelos to the Pentateuch: A Collection of Fragments in the Library of the Jewish Theological Seminary תרגום אונקלוס על התורה... אוסף קטעים בספרית בית המדרש לרבנים באמריקה From Naples to Constantinople: the Aesop workshop’s woodcuts in the oldest illustrated printed Haggadah בויארין, דניאל Boyarin, Daniel---The Library The Library 'From Naples to Constantinople: the Aesop workshop's woodcuts in  the oldest illustrated printed Haggadah' Frojmovic, Eva---The Library The Library From Naples to Constantinople: the Aesop workshop’s woodcuts in the oldest illustrated printed Haggadah</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="130" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -759,11 +943,31 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>פרשנות מקרא. ; Biblical Exegesis: Exodus 24:10 – 25:12 ; פרשנות מקרא: שמות כד:י – כה:יב</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>קטלוג ליברמן Lieberman Catalog</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="130" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -790,11 +994,31 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>MEAH Aproximacion a la lengua de Shir ha-Shirim Rabba y modelo de edicion חירון-בלנק, לואיס פ. Girón Blanc, Luis-Fernando---A Catalogue of Fragments of Halakhah and Midrash from the Cairo Genizah in the Elkan Nathan Adler Collection קטלוג של שרידי הלכה ומדרש מגניזת-קאהיר באוסף א"נ אדלר  דנציג, נחמן Danzig, Neil</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -821,11 +1045,31 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>פרשנות מקרא. ; Biblical Exegesis: Exodus 18; 20 ; פרשנות מקרא: שמות יח; כ</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>קטלוג ליברמן Lieberman Catalog</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="130" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -852,11 +1096,31 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
+          <t>Doubtful if genizah, Identifications' details are currently unavailable ; ספק גניזה, אין בידנו לעת עתה פרטים על תוכנו של הקטע</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Catalogue of the Hebrew manuscripts in the Bodleian Library קטלוג נויבאואר-קאולי Neubauer Cowley Catalog Cowley, Arthur Ernest &amp; Neubauer, Adolf</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="130" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -883,11 +1147,31 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>Doubtful if genizah, Identifications' details are currently unavailable ; ספק גניזה, אין בידנו לעת עתה פרטים על תוכנו של הקטע</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Catalogue of the Hebrew manuscripts in the Bodleian Library קטלוג נויבאואר-קאולי Neubauer Cowley Catalog Cowley, Arthur Ernest &amp; Neubauer, Adolf</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>MODEL PATH: this row failed the mechanical heuristic name-match (it is part of the residual) and the pinned gate (gemini-3.6-flash, effort=low) classified it `fills_gap` -- it WOULD ship as a 'Candidate for new finds' in production.</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="130" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -914,11 +1198,31 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="130" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -945,11 +1249,31 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="130" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -976,11 +1300,31 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="130" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1007,11 +1351,31 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="130" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1038,11 +1402,31 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="130" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1069,11 +1453,31 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="130" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1100,11 +1504,31 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="130" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1131,11 +1555,31 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="130" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -1162,11 +1606,31 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="130" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -1193,11 +1657,31 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="130" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -1224,11 +1708,31 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="130" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -1255,11 +1759,31 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="130" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -1286,11 +1810,31 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="130" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -1317,11 +1861,31 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="130" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -1348,11 +1912,31 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="130" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -1379,11 +1963,31 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="130" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -1410,11 +2014,31 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="130" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -1441,11 +2065,31 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="130" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -1472,11 +2116,31 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="130" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -1503,12 +2167,32 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>(none -- this source has no text at all for this manuscript)</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
           <t>BYPASS PATH: NONE of the four checked-source families (catalogue, bibliography, PGP, FGP) has ANY text at all for this manuscript -- this row ships as a 'Candidate for new finds' automatically, with NOTHING checked against it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G34"/>
+  <autoFilter ref="A1:K34"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid verdict" error="Choose 'genuinely_novel', 'actually_recorded', 'unsure' or 'skip'. Free text is rejected." promptTitle="Verdict" prompt="Is this fragment genuinely not identified in the finding aids we checked? Blank = not yet answered." type="list">
       <formula1>"genuinely_novel,actually_recorded,unsure,skip"</formula1>
